--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:02+00:00</t>
+    <t>2026-06-29T12:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:39:39+00:00</t>
+    <t>2026-07-21T11:52:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T11:52:46+00:00</t>
+    <t>2026-07-21T11:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T11:54:41+00:00</t>
+    <t>2026-07-21T12:00:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:00:27+00:00</t>
+    <t>2026-07-27T13:17:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:17:31+00:00</t>
+    <t>2026-07-27T13:23:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:23:52+00:00</t>
+    <t>2026-07-27T13:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:42:38+00:00</t>
+    <t>2026-07-27T13:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:52:49+00:00</t>
+    <t>2026-07-27T13:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:55:37+00:00</t>
+    <t>2026-07-27T16:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T16:09:25+00:00</t>
+    <t>2026-07-28T08:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
